--- a/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-其他）.xlsx
+++ b/internal_doc/05.测试设计/story/民生银行资源管控/Story-民生银行资源管控测试用例（资源监控-其他）.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
   <si>
     <t>name</t>
   </si>
@@ -49,10 +49,6 @@
   </si>
   <si>
     <t>execution_type2</t>
-  </si>
-  <si>
-    <t>重复多次执行定时脚本</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>1、重复多次执行定时脚本
@@ -60,20 +56,124 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>执行定时脚本获取监控信息</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、执行定时脚本获取监控信息
+    <t>1、执行成功，任务按指定周期定时采集快照的数据并成功写入CL，周期正确，写入到CL的数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、重复执行，执行失败，提示任务已在运行，提示信息合理准确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>配置定时任务定时采集数据</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>重复多次执行定时脚本（本机或集群下多个主机）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中CL被删除</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中数据主节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中编目主节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中协调节点异常</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中CPU占用率100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>数据采集过程中内存占用率100%</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、配置定时任务配置文件，配置正确
 2、检查任务执行情况</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>1、执行成功，任务按指定周期定时采集快照的数据并成功写入CL，周期正确，写入到CL的数据正确</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1、重复执行，执行失败，提示任务已在运行，提示信息合理准确</t>
+    <t>定时任务已下发，数据正在定时被采集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>删除定时任务</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据采集过程中模拟数据主节点异常，如：节点被异常停止
+2、检查采集结果，包括采集数据和日志
+（重复多次模拟该场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、采集失败，提示数据主节点异常，提示信息合理准确，其中采集失败的之前的任务采集的数据正确（如第n个周期采集失败，n之前的周期数据不影响）
+2、故障恢复后定时任务继续采集，采集周期和数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据采集过程中模拟编目主节点异常，如：节点被异常停止
+2、检查采集结果，包括采集数据和日志
+（重复多次模拟该场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、采集失败，提示节点异常，提示信息合理准确，其中采集失败的之前的任务采集的数据正确（如第n个周期采集失败，n之前的周期数据不影响）
+2、故障恢复后定时任务继续采集，采集周期和数据正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据采集过程中模拟协调节点异常，如：节点被异常停止
+2、检查采集结果，包括采集数据和日志
+（重复多次模拟该场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据采集过程中模拟CPU占用率100%（如使用eatcpu工具），执行./eatcpu
+2、检查采集结果，包括采集数据和日志
+（重复多次模拟该场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、数据采集过程中模拟内存占用率100%（如：使用eatmem工具，执行./eatmem -m 100）
+2、检查采集结果，包括采集数据和日志
+（重复多次模拟该场景）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、采集成功/失败，采集成功则周期和数据正确，采集失败则故障恢复后能正常采集</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、修改配置文件删除定时配置项
+2、检查采集结果</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、定时任务被删除，数据停止采集
+2、重新添加配置项后数据再次按周期采集，采集周期和结果正确</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>定时任务长时间运行（超过12/24小时）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、配置定时任务配置文件，配置正确
+2、任务定时采集后让其运行12小时以上，检查任务执行情况</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1、任务长时间运行正常
+2、采集周期和数据正确，包括跨零点和跨月的时间点前后采集周期和数据正确（存放采集数据的集合为主子表，且按月创建子表，需要检查主子表零点/跨月时间点数据正确性）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -223,8 +323,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I5" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
-  <autoFilter ref="A1:I5"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表1" displayName="表1" ref="A1:I11" tableType="xml" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" connectionId="1">
+  <autoFilter ref="A1:I11"/>
   <tableColumns count="9">
     <tableColumn id="1" uniqueName="name" name="name" dataDxfId="8">
       <xmlColumnPr mapId="1" xpath="/testcases/testcase/@name" xmlDataType="string"/>
@@ -543,7 +643,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="34.5" style="1" customWidth="1"/>
@@ -587,7 +687,7 @@
     </row>
     <row r="2" spans="1:9" ht="40.5">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" s="3">
         <v>1</v>
@@ -599,10 +699,10 @@
         <v>1</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="I2" s="3">
         <v>1</v>
@@ -610,28 +710,34 @@
     </row>
     <row r="3" spans="1:9" ht="27">
       <c r="A3" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="D3" s="3">
-        <v>1</v>
-      </c>
-      <c r="E3" s="3">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3">
-        <v>1</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>10</v>
-      </c>
       <c r="H3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="81">
+      <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="I3" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D4" s="3">
         <v>1</v>
       </c>
@@ -641,15 +747,24 @@
       <c r="F4" s="3">
         <v>1</v>
       </c>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>24</v>
+      </c>
       <c r="I4" s="3">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="3"/>
+    <row r="5" spans="1:9" ht="81">
+      <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
       <c r="B5" s="5"/>
+      <c r="C5" s="1" t="s">
+        <v>21</v>
+      </c>
       <c r="D5" s="3">
         <v>1</v>
       </c>
@@ -659,9 +774,173 @@
       <c r="F5" s="3">
         <v>1</v>
       </c>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>26</v>
+      </c>
       <c r="I5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="81">
+      <c r="A6" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B6" s="5"/>
+      <c r="C6" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="3">
+        <v>1</v>
+      </c>
+      <c r="E6" s="3">
+        <v>2</v>
+      </c>
+      <c r="F6" s="3">
+        <v>1</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I6" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="81">
+      <c r="A7" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="5"/>
+      <c r="C7" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D7" s="3">
+        <v>1</v>
+      </c>
+      <c r="E7" s="3">
+        <v>2</v>
+      </c>
+      <c r="F7" s="3">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="I7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="54">
+      <c r="A8" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="5"/>
+      <c r="C8" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D8" s="3">
+        <v>1</v>
+      </c>
+      <c r="E8" s="3">
+        <v>2</v>
+      </c>
+      <c r="F8" s="3">
+        <v>1</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="54">
+      <c r="A9" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="5"/>
+      <c r="C9" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D9" s="3">
+        <v>1</v>
+      </c>
+      <c r="E9" s="3">
+        <v>2</v>
+      </c>
+      <c r="F9" s="3">
+        <v>1</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="I9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="40.5">
+      <c r="A10" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10" s="5"/>
+      <c r="C10" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D10" s="3">
+        <v>1</v>
+      </c>
+      <c r="E10" s="3">
+        <v>2</v>
+      </c>
+      <c r="F10" s="3">
+        <v>1</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I10" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="81">
+      <c r="A11" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B11" s="5"/>
+      <c r="C11" s="3"/>
+      <c r="D11" s="3">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <v>2</v>
+      </c>
+      <c r="F11" s="3">
+        <v>1</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="I11" s="3">
         <v>1</v>
       </c>
     </row>
